--- a/docs/ingestion/CPQ_XML_CONFIRM_RESOLVE_PERFORMANCE_ISSUES_2026-10-04.xlsx
+++ b/docs/ingestion/CPQ_XML_CONFIRM_RESOLVE_PERFORMANCE_ISSUES_2026-10-04.xlsx
@@ -48,7 +48,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE599"/>
+        <bgColor rgb="00FFE599"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,16 +177,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -585,7 +591,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Implemented on branch fix/cpq-xml-confirm-performance-2026-10-04 -- Issues #0 (partial), #1, #2, #3 (partial), #6, #7, #8 are code, not just designs (see each row's Fix Design column). #3b and #4 remain designs only, exactly as originally recommended (most invasive change / needs live profiling first, respectively).</t>
+          <t>Implemented on branch fix/cpq-xml-confirm-performance-2026-10-04 -- every issue is now code, not just a design (see each row's Fix Design column). #3b shipped opt-in/default-off (ARYX_CPQ_STREAMING_PROJECTION_ENABLED) since it's the most invasive change and unverified against a real large file; #4 shipped partial (diagnostic tooling + one low-risk index) since the real root cause still needs live Oracle profiling this environment can't do.</t>
         </is>
       </c>
     </row>
@@ -961,7 +967,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Fix designed only</t>
+          <t>Implemented (opt-in, default off)</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -971,15 +977,17 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Stream grouped-by-tag, not the whole document, in two parts:
-1) Convert project_xml_to_raw_graph() to a generator (iter_raw_graph_nodes) yielding each finished RawNode/RawEdge as its element ends (iterparse already visits in document order) -- peak memory becomes O(nesting depth) for the walk itself.
-2) resolve_and_relate_raw_graph() groups-and-flushes per tag incrementally from that generator instead of grouping a fully-materialized projection -- removes the current DOUBLE retention (full projection + group_nodes_by_tag's regrouping) down to one structure. For further headroom, per-tag lists could spill to a PgChunkBackend-style temp store once a size threshold is crossed.
-More invasive than #1/#2 (touches the parser's public contract) -- scope as its own follow-up PR, not bundled with the others.</t>
+          <t>IMPLEMENTED, opt-in (ARYX_CPQ_STREAMING_PROJECTION_ENABLED, default false) -- most invasive change in the doc, no live-run verification yet:
+1) New iter_raw_graph() generator in xml_projector.py, yielding each finished RawNode + its one parent edge as its element ends -- peak memory becomes O(nesting depth) for the walk itself. project_xml_to_raw_graph() itself is unchanged and stays the default for every other caller.
+2) structural_leaf.py's fold_structural_leaf_tags decoupled from RawGraphProjection (takes edges + by_tag directly) so both eager and streaming paths share it.
+3) resolve_and_relate_raw_graph() accepts xml_bytes as an alternative to projection; when the flag is on, builds by_tag incrementally from the generator instead of a fully-materialized projection -- removes the double node-list retention. Falls back to the eager path automatically when ARYX_CSV_BML_ENABLED is also on (no streaming equivalent for that enrichment).
+4) doc_discovery.py's cpq loop now passes xml_bytes directly; the eager-vs-streaming decision lives entirely in resolve_and_relate_raw_graph().
+Still needed: a real large-file confirm run comparing entity/relationship counts and peak memory between the two paths before flipping the default on.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>src/aryx/cpq_ingestion/raw_graph/xml_projector.py; src/aryx/cpq_ingestion/raw_graph/resolve_relate.py</t>
+          <t>src/aryx/cpq_ingestion/raw_graph/xml_projector.py; src/aryx/cpq_ingestion/raw_graph/structural_leaf.py; src/aryx/cpq_ingestion/raw_graph/resolve_relate.py; src/aryx/pipeline/doc_discovery/doc_discovery.py; src/aryx/config/config_core.py</t>
         </is>
       </c>
     </row>
@@ -1004,9 +1012,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Fix designed only</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Implemented (partial)</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1016,13 +1024,15 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Step 1 (diagnosis gap, must happen first): capture actual SQL text + EXPLAIN PLAN / DBMS_XPLAN for the slow select, re-measure with no confirm job running concurrently to separate genuine slow query from contention.
-Step 2 (conditional): if a scan is found, add a composite index matching the workspace-scoped filter predicate; if it's contention, route interactive UI reads to a less-contended connection pool/replica. Independent of #1-#3b, can be scoped and fixed on its own schedule.</t>
+          <t>Step 1 (diagnosis) genuinely can't be done from this environment -- no live Oracle ADB session to run EXPLAIN PLAN against. IMPLEMENTED instead:
+1) Automatic plan capture: oracle_cursor.py's _log_stmt_ok() now runs a best-effort EXPLAIN PLAN FOR &lt;sql&gt; + DBMS_XPLAN.DISPLAY on a FRESH cursor (never the statement's own, to avoid discarding its unfetched result set) whenever a statement crosses the slow threshold, included in the existing db.oracle.slow_statement log event. Turns Step 1 into 'already captured, next time it happens.'
+2) One speculative, low-risk fix: new migration 0049 adds idx_datasource_ws_created (workspace_id, created_at DESC) -- a genuine covering index for select_datasources.sql's exact WHERE+ORDER BY shape, confirmed as the source of the SELECT aryx_datasource evidence rows. NOT presented as a confirmed fix for the observed durations -- contention from the concurrent confirm job remains an equally live, unaddressed hypothesis.
+3) NOT implemented: the connection-pool-separation idea -- a real architectural change that deserves its own scoped PR once captured plan data says contention, not a bad plan, is the actual cause.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>src/aryx/queries/*.sql (oracle variants); connection pool config</t>
+          <t>src/aryx/store/oracle_cursor.py; src/aryx/store/migrations/0049_datasource_ws_created_idx.sql (+ oracle variant)</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1402,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>⬜ Stream the raw-graph projection by tag instead of materializing the whole document</t>
+          <t>🟨 Stream the raw-graph projection by tag instead of materializing the whole document</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1436,7 +1446,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>⬜ Profile and fix the slow Oracle queries on UI endpoints</t>
+          <t>🟨 Profile and fix the slow Oracle queries on UI endpoints</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
